--- a/data/trans_camb/P2A_senso_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,31</t>
+          <t>-2,59; 0,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; -0,26</t>
+          <t>-3,16; -0,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,85</t>
+          <t>-1,76; 1,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,04</t>
+          <t>-1,39; 0,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,24</t>
+          <t>-2,1; 0,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,97</t>
+          <t>1,71; 4,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,27</t>
+          <t>-1,68; 0,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; -0,3</t>
+          <t>-2,28; -0,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,23</t>
+          <t>0,68; 3,2</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,79; 14,98</t>
+          <t>-63,73; 13,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-77,33; -8,89</t>
+          <t>-77,36; -6,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 70,75</t>
+          <t>-44,13; 74,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 54,03</t>
+          <t>-43,89; 48,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,44; 16,26</t>
+          <t>-68,07; 24,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,38; 238,04</t>
+          <t>50,12; 256,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,93; 11,86</t>
+          <t>-48,38; 11,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,34; -9,72</t>
+          <t>-66,04; -15,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,1; 129,49</t>
+          <t>20,28; 132,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,57</t>
+          <t>0,12; 1,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,79</t>
+          <t>-0,4; 0,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,17</t>
+          <t>0,48; 2,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,57</t>
+          <t>-0,16; 1,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,57</t>
+          <t>-0,73; 0,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 34,91</t>
+          <t>0,98; 31,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,27</t>
+          <t>0,18; 1,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,58</t>
+          <t>-0,37; 0,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 21,76</t>
+          <t>1,1; 20,84</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 334,32</t>
+          <t>6,79; 379,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,36; 171,71</t>
+          <t>-44,88; 203,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,51; 465,05</t>
+          <t>38,53; 460,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 212,62</t>
+          <t>-19,14; 187,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,46; 85,99</t>
+          <t>-51,43; 86,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,45; 4773,45</t>
+          <t>76,73; 4397,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,16; 197,99</t>
+          <t>16,17; 191,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 94,22</t>
+          <t>-33,87; 78,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>112,44; 3300,76</t>
+          <t>118,06; 2795,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,45</t>
+          <t>-0,52; 2,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,9</t>
+          <t>-1,22; 0,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,43</t>
+          <t>-0,2; 2,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,81</t>
+          <t>0,43; 4,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,14</t>
+          <t>-1,94; 0,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,62</t>
+          <t>-0,83; 1,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,95</t>
+          <t>0,33; 2,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,38</t>
+          <t>-1,19; 0,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,62</t>
+          <t>0,02; 1,71</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-79,34; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,43; 991,39</t>
+          <t>-38,24; 973,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,35; 1086,02</t>
+          <t>0,13; 890,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 146,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 430,87</t>
+          <t>-48,69; 381,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,96; 582,16</t>
+          <t>16,28; 669,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,63; 111,97</t>
+          <t>-82,75; 83,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 346,16</t>
+          <t>-7,02; 342,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,79</t>
+          <t>-0,45; 0,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; -0,02</t>
+          <t>-1,06; 0,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,38</t>
+          <t>-0,05; 1,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,2</t>
+          <t>-0,14; 1,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; -0,08</t>
+          <t>-1,18; 0,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 24,35</t>
+          <t>1,04; 23,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,77</t>
+          <t>-0,14; 0,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; -0,15</t>
+          <t>-0,94; -0,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 13,78</t>
+          <t>0,82; 15,57</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 63,12</t>
+          <t>-25,67; 66,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-58,53; -0,65</t>
+          <t>-57,97; 9,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 106,2</t>
+          <t>-3,46; 106,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 83,49</t>
+          <t>-7,91; 84,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,46; -3,25</t>
+          <t>-58,94; 1,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,11; 1892,26</t>
+          <t>58,34; 1906,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 53,2</t>
+          <t>-7,19; 58,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,44; -10,48</t>
+          <t>-52,54; -12,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>47,04; 861,16</t>
+          <t>51,75; 1029,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_senso_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>1,97</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,27</t>
+          <t>-2,63; 0,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; -0,23</t>
+          <t>-3,21; -0,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,86</t>
+          <t>-1,93; 1,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,91</t>
+          <t>-1,44; 0,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,44</t>
+          <t>-2,32; 0,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,86</t>
+          <t>2,04; 5,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,29</t>
+          <t>-1,61; 0,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; -0,42</t>
+          <t>-2,25; -0,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,2</t>
+          <t>0,85; 3,14</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-2,53%</t>
+          <t>-6,35%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>128,53%</t>
+          <t>135,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>67,23%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-63,73; 13,47</t>
+          <t>-62,05; 11,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-77,36; -6,19</t>
+          <t>-77,73; -7,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,13; 74,47</t>
+          <t>-47,26; 63,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,89; 48,29</t>
+          <t>-44,28; 44,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,07; 24,44</t>
+          <t>-69,55; 8,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,12; 256,69</t>
+          <t>61,67; 259,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,38; 11,62</t>
+          <t>-48,79; 10,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,04; -15,83</t>
+          <t>-67,08; -14,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,28; 132,5</t>
+          <t>23,12; 124,83</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,18</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>1,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,53</t>
+          <t>0,12; 1,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,82</t>
+          <t>-0,5; 0,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,24</t>
+          <t>1,04; 2,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,48</t>
+          <t>-0,13; 1,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,55</t>
+          <t>-0,74; 0,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 31,86</t>
+          <t>0,74; 2,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,23</t>
+          <t>0,17; 1,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,53</t>
+          <t>-0,44; 0,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 20,84</t>
+          <t>1,17; 2,29</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>188,37%</t>
+          <t>252,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>965,3%</t>
+          <t>147,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>649,12%</t>
+          <t>191,71%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 379,84</t>
+          <t>6,37; 364,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,88; 203,56</t>
+          <t>-52,21; 180,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,53; 460,55</t>
+          <t>89,41; 616,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 187,5</t>
+          <t>-14,65; 222,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,43; 86,32</t>
+          <t>-52,42; 102,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,73; 4397,69</t>
+          <t>48,77; 397,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,17; 191,08</t>
+          <t>12,23; 201,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,87; 78,96</t>
+          <t>-37,85; 77,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>118,06; 2795,76</t>
+          <t>101,09; 356,04</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,92</t>
+          <t>-0,53; 2,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,9</t>
+          <t>-1,08; 0,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,4</t>
+          <t>-0,17; 2,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,91</t>
+          <t>0,52; 4,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,11</t>
+          <t>-1,91; 0,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,65</t>
+          <t>-0,58; 1,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,89</t>
+          <t>0,34; 2,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,31</t>
+          <t>-1,17; 0,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,71</t>
+          <t>-0,03; 1,7</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149,25%</t>
+          <t>141,03%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>101,59%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-79,34; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 973,81</t>
+          <t>-31,13; 979,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 890,88</t>
+          <t>3,87; 1013,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,69; 381,9</t>
+          <t>-35,85; 644,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,28; 669,79</t>
+          <t>10,46; 623,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,75; 83,22</t>
+          <t>-86,27; 131,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 342,96</t>
+          <t>-10,75; 379,95</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>1,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,82</t>
+          <t>-0,47; 0,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,08</t>
+          <t>-1,1; 0,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,36</t>
+          <t>0,26; 1,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,14</t>
+          <t>-0,15; 1,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,01</t>
+          <t>-1,19; -0,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 23,7</t>
+          <t>0,89; 2,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,79</t>
+          <t>-0,16; 0,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; -0,17</t>
+          <t>-1,0; -0,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 15,57</t>
+          <t>0,77; 1,74</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>406,91%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>236,2%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 66,1</t>
+          <t>-25,82; 63,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,97; 9,44</t>
+          <t>-58,03; 5,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 106,96</t>
+          <t>13,75; 134,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 84,72</t>
+          <t>-8,22; 86,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,94; 1,55</t>
+          <t>-58,42; -1,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,34; 1906,64</t>
+          <t>42,81; 161,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 58,19</t>
+          <t>-9,13; 57,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,54; -12,8</t>
+          <t>-53,91; -9,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51,75; 1029,83</t>
+          <t>41,3; 128,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_senso_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
